--- a/design/templates/generated/Uva/POTABLE_WATER_LANDSLIDE_UVA_V1_upload_template.xlsx
+++ b/design/templates/generated/Uva/POTABLE_WATER_LANDSLIDE_UVA_V1_upload_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2021-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-2030" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEIGHTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_META" sheetId="5" state="hidden" r:id="rId5"/>
@@ -559,7 +559,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2020-2025 - Water Sector / Potable Water - Landslide - Uva Province   [profile POTABLE_WATER_LANDSLIDE_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2021-2025 - Water Sector / Potable Water - Landslide - Uva Province   [profile POTABLE_WATER_LANDSLIDE_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2025</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2020-2025</t>
+          <t>Dept. report 2021-2025</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>UVA-001</t>
+          <t>BA1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2025</v>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>UVA-002</t>
+          <t>BA2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2025</v>
@@ -915,7 +915,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>UVA-003</t>
+          <t>BA3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2025</v>
@@ -952,7 +952,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>UVA-004</t>
+          <t>BA4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2025</v>
@@ -989,12 +989,12 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>UVA-005</t>
+          <t>BA5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Hali-Ela</t>
+          <t>Hali-ela</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2025</v>
@@ -1026,7 +1026,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>UVA-006</t>
+          <t>BA6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2025</v>
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>UVA-007</t>
+          <t>BA7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2025</v>
@@ -1100,7 +1100,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>UVA-008</t>
+          <t>BA8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2025</v>
@@ -1137,7 +1137,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>UVA-009</t>
+          <t>BA9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2025</v>
@@ -1174,7 +1174,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>UVA-010</t>
+          <t>BA10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2025</v>
@@ -1211,7 +1211,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>UVA-011</t>
+          <t>BA11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2025</v>
@@ -1248,7 +1248,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>UVA-012</t>
+          <t>BA12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2025</v>
@@ -1285,7 +1285,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>UVA-013</t>
+          <t>BA13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2025</v>
@@ -1322,7 +1322,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>UVA-014</t>
+          <t>BA14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2025</v>
@@ -1359,7 +1359,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>UVA-015</t>
+          <t>BA15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2025</v>
@@ -1396,7 +1396,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>UVA-016</t>
+          <t>MO1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2025</v>
@@ -1433,7 +1433,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>UVA-017</t>
+          <t>MO2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2025</v>
@@ -1470,7 +1470,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>UVA-018</t>
+          <t>MO3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2025</v>
@@ -1507,7 +1507,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>UVA-019</t>
+          <t>MO4</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2025</v>
@@ -1544,7 +1544,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>UVA-020</t>
+          <t>MO5</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2025</v>
@@ -1581,7 +1581,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>UVA-021</t>
+          <t>MO6</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2025</v>
@@ -1618,7 +1618,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>UVA-022</t>
+          <t>MO7</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2025</v>
@@ -1655,7 +1655,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>UVA-023</t>
+          <t>MO8</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2025</v>
@@ -1692,7 +1692,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>UVA-024</t>
+          <t>MO9</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2025</v>
@@ -1729,7 +1729,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>UVA-025</t>
+          <t>MO10</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2025</v>
@@ -1766,7 +1766,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>UVA-026</t>
+          <t>MO11</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2025</v>
@@ -1801,7 +1801,6 @@
       <c r="S30" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
@@ -1847,7 +1846,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2025-2030 - Water Sector / Potable Water - Landslide - Uva Province   [profile POTABLE_WATER_LANDSLIDE_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2026-2030 - Water Sector / Potable Water - Landslide - Uva Province   [profile POTABLE_WATER_LANDSLIDE_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2073,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2030</v>
@@ -2117,7 +2116,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2025-2030</t>
+          <t>Dept. report 2026-2030</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -2129,7 +2128,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>UVA-001</t>
+          <t>BA1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -2143,7 +2142,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2030</v>
@@ -2166,7 +2165,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>UVA-002</t>
+          <t>BA2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2180,7 +2179,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2030</v>
@@ -2203,7 +2202,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>UVA-003</t>
+          <t>BA3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2217,7 +2216,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2030</v>
@@ -2240,7 +2239,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>UVA-004</t>
+          <t>BA4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2254,7 +2253,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2030</v>
@@ -2277,12 +2276,12 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>UVA-005</t>
+          <t>BA5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Hali-Ela</t>
+          <t>Hali-ela</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -2291,7 +2290,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2030</v>
@@ -2314,7 +2313,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>UVA-006</t>
+          <t>BA6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2328,7 +2327,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2030</v>
@@ -2351,7 +2350,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>UVA-007</t>
+          <t>BA7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -2365,7 +2364,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2030</v>
@@ -2388,7 +2387,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>UVA-008</t>
+          <t>BA8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2402,7 +2401,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2030</v>
@@ -2425,7 +2424,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>UVA-009</t>
+          <t>BA9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -2439,7 +2438,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2030</v>
@@ -2462,7 +2461,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>UVA-010</t>
+          <t>BA10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2476,7 +2475,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2030</v>
@@ -2499,7 +2498,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>UVA-011</t>
+          <t>BA11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -2513,7 +2512,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2030</v>
@@ -2536,7 +2535,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>UVA-012</t>
+          <t>BA12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -2550,7 +2549,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2030</v>
@@ -2573,7 +2572,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>UVA-013</t>
+          <t>BA13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -2587,7 +2586,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2030</v>
@@ -2610,7 +2609,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>UVA-014</t>
+          <t>BA14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -2624,7 +2623,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2030</v>
@@ -2647,7 +2646,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>UVA-015</t>
+          <t>BA15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -2661,7 +2660,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2030</v>
@@ -2684,7 +2683,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>UVA-016</t>
+          <t>MO1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -2698,7 +2697,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2030</v>
@@ -2721,7 +2720,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>UVA-017</t>
+          <t>MO2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -2735,7 +2734,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2030</v>
@@ -2758,7 +2757,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>UVA-018</t>
+          <t>MO3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -2772,7 +2771,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2030</v>
@@ -2795,7 +2794,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>UVA-019</t>
+          <t>MO4</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -2809,7 +2808,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2030</v>
@@ -2832,7 +2831,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>UVA-020</t>
+          <t>MO5</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -2846,7 +2845,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2030</v>
@@ -2869,7 +2868,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>UVA-021</t>
+          <t>MO6</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2883,7 +2882,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2030</v>
@@ -2906,7 +2905,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>UVA-022</t>
+          <t>MO7</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -2920,7 +2919,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2030</v>
@@ -2943,7 +2942,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>UVA-023</t>
+          <t>MO8</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2957,7 +2956,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2030</v>
@@ -2980,7 +2979,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>UVA-024</t>
+          <t>MO9</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2994,7 +2993,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2030</v>
@@ -3017,7 +3016,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>UVA-025</t>
+          <t>MO10</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -3031,7 +3030,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2030</v>
@@ -3054,7 +3053,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>UVA-026</t>
+          <t>MO11</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -3068,7 +3067,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2030</v>
@@ -3089,7 +3088,6 @@
       <c r="S30" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
@@ -3108,7 +3106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3117,6 +3115,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3164,6 +3163,11 @@
           <t>PROPOSED WEIGHT % (read at import)</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>basis of the proposal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -3184,6 +3188,7 @@
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="12" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -3204,6 +3209,7 @@
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
+      <c r="G5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -3232,6 +3238,7 @@
       <c r="F6" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="G6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -3252,6 +3259,7 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
+      <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -3280,6 +3288,7 @@
       <c r="F8" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -3308,6 +3317,7 @@
       <c r="F9" s="12" t="n">
         <v>15</v>
       </c>
+      <c r="G9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -3336,6 +3346,7 @@
       <c r="F10" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -3364,6 +3375,7 @@
       <c r="F11" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -3392,6 +3404,7 @@
       <c r="F12" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -3412,6 +3425,7 @@
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
+      <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -3440,6 +3454,7 @@
       <c r="F14" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -3468,6 +3483,7 @@
       <c r="F15" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G15" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -3492,9 +3508,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
@@ -3533,14 +3548,14 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: POTABLE_WATER_LANDSLIDE_UVA_V1   |   generated 2026-07-29 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: POTABLE_WATER_LANDSLIDE_UVA_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. One tab per data period (2020-2025, 2025-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
+          <t>1. One tab per data period (2021-2025, 2026-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
         </is>
       </c>
     </row>
@@ -3554,14 +3569,14 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2b. The year 2025 appears in both tabs. If a year sits in two periods the system uses the LATER period's value, so nothing is counted twice.</t>
+          <t>2b. The two periods are contiguous and do not overlap (changed 2026-09-03 at the Central panel's request - the old 2020-2025 / 2025-2030 pair shared the year 2025 and needed a tie-break). Every year belongs to exactly one tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>3. Edit ONLY the yellow cells. Division codes, names, district and the period columns are pre-filled and locked.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3590,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Do not add, remove, rename or reorder columns or tabs. Files with changed structure are rejected on import.</t>
+          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4081,80 +4096,104 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>generated</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>unlocked-review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dsd_level</t>
+          <t>panel_overrides</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>DS_DIVISION</t>
+          <t>0 add, 0 retire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>periods</t>
+          <t>generated</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2020-2025|2025-2030</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>n_variables</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>12</v>
+          <t>dsd_level</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>DS_DIVISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>period_rule_default</t>
+          <t>periods</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>average (typical year); 2025 -&gt; latest period wins</t>
+          <t>2021-2025|2026-2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>period_aggregation</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>CUTTING_FAILURES_EARTH_SLIPS_2000_TO_2023=fixed_window|LANDSLIDE_EVENTS_1974_TO_2023=fixed_window|LANDSLIDE_HAZARD_INDEX=fixed_window|VERY_WET_DAYS=average|BUILDINGS_LANDSLIDE_AFFECTED_AREA=average|LANDSLIDE_AFFECTED_AREA=average|MAXIMUM_LANDSLIDE_AFFECTED_PEOPLE_DURING_1974_TO_2023=max|PCT_HH_FED_BY_WELLS=average|PCT_HH_RURAL_WATER_SUPPLY=average|PCT_LANDSLIDE_AFFECTED_AREA=average|POPULATION_DENSITY=average|WATER_INTAKE_POINTS=average</t>
-        </is>
+          <t>n_variables</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>period_rule_default</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>average (typical year); periods are contiguous, no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>period_aggregation</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>CUTTING_FAILURES_EARTH_SLIPS_2000_TO_2023=fixed_window|LANDSLIDE_EVENTS_1974_TO_2023=fixed_window|LANDSLIDE_HAZARD_INDEX=fixed_window|VERY_WET_DAYS=average|BUILDINGS_LANDSLIDE_AFFECTED_AREA=average|LANDSLIDE_AFFECTED_AREA=average|MAXIMUM_LANDSLIDE_AFFECTED_PEOPLE_DURING_1974_TO_2023=max|PCT_HH_FED_BY_WELLS=average|PCT_HH_RURAL_WATER_SUPPLY=average|PCT_LANDSLIDE_AFFECTED_AREA=average|POPULATION_DENSITY=average|WATER_INTAKE_POINTS=average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>expected_columns</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|CUTTING_FAILURES_EARTH_SLIPS_2000_TO_2023|LANDSLIDE_EVENTS_1974_TO_2023|LANDSLIDE_HAZARD_INDEX|VERY_WET_DAYS|BUILDINGS_LANDSLIDE_AFFECTED_AREA|LANDSLIDE_AFFECTED_AREA|MAXIMUM_LANDSLIDE_AFFECTED_PEOPLE_DURING_1974_TO_2023|PCT_HH_FED_BY_WELLS|PCT_HH_RURAL_WATER_SUPPLY|PCT_LANDSLIDE_AFFECTED_AREA|POPULATION_DENSITY|WATER_INTAKE_POINTS|DATA_SOURCE|NOTES</t>
         </is>

--- a/design/templates/generated/Uva/POTABLE_WATER_LANDSLIDE_UVA_V1_upload_template.xlsx
+++ b/design/templates/generated/Uva/POTABLE_WATER_LANDSLIDE_UVA_V1_upload_template.xlsx
@@ -3548,7 +3548,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: POTABLE_WATER_LANDSLIDE_UVA_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: POTABLE_WATER_LANDSLIDE_UVA_V1   |   generated 2026-09-14 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
@@ -3574,9 +3574,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>3. The yellow cells are where data belongs. Division codes, names, district and the period columns are pre-filled - change one only to correct a genuine error. Nothing in this file is protected, so please treat that as the instruction it is; the importer checks those columns and will refuse what it cannot match.</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
+          <t>5. Do not add, remove, rename or reorder columns or tabs. Excel will now let you - the sheet is not protected - but the importer will not: the hidden _META tab states this file's column contract and a file whose structure has changed is refused, naming what changed. Nothing loads partially, so a rejected file loads nothing at all.</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>unlocked-review</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
